--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="8664"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="8784"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,25 +16,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>2DObject/SkillObject_Projectile_Banana</x:t>
   </x:si>
   <x:si>
-    <x:t>2DObject/SkillObject_Projectile_Banana</x:t>
+    <x:t>2DObject/SkillObject_Projectile_Apple</x:t>
   </x:si>
   <x:si>
     <x:t>사과를 날린다.</x:t>
   </x:si>
   <x:si>
-    <x:t>2DObject/SkillObject_Projectile_Apple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_appleShot_01</x:t>
+    <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
@@ -43,16 +37,22 @@
     <x:t>바나나를 날린다.</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_appleShot_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_bananaShot_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>사과 날리기</x:t>
@@ -939,42 +939,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>13</x:v>
@@ -983,7 +983,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="3"/>
       <x:c r="F4" s="3"/>
@@ -999,16 +999,16 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="3"/>
       <x:c r="F5" s="3"/>
